--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_07-03-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_07-03-2026.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>£13.07</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -966,7 +966,36 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>£19.65</t>
+          <t xml:space="preserve">Error: Message: timeout: Timed out receiving message from renderer: 298.918
+  (Session info: chrome=145.0.7632.160)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff62bd0aa55
+	0x7ff62ba68630
+	0x7ff62b7fd75d
+	0x7ff62b7ea3d9
+	0x7ff62b7ea0c1
+	0x7ff62b7e7d0b
+	0x7ff62b7e862f
+	0x7ff62b7f7b0a
+	0x7ff62b80e9f7
+	0x7ff62b81612a
+	0x7ff62b7e8df1
+	0x7ff62b80e72b
+	0x7ff62b8a5cc1
+	0x7ff62b849098
+	0x7ff62b849f83
+	0x7ff62bd37810
+	0x7ff62bd31afd
+	0x7ff62bd52c1a
+	0x7ff62ba83345
+	0x7ff62ba8b81c
+	0x7ff62ba71924
+	0x7ff62ba71ad6
+	0x7ff62ba57e47
+	0x7ffe0db5e8d7
+	0x7ffe0f12c40c
+</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1386,7 +1415,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>£27.20</t>
+          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Max retries exceeded with url: /product/100mm-celotex-ga4100-pir-insulation-board-2400x1200mm/ (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001EE41B93D10&gt;, 'Connection to www.onlineinsulation-sales.com timed out. (connect timeout=30)'))</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1610,7 +1639,36 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>£32.98</t>
+          <t xml:space="preserve">Error: Message: timeout: Timed out receiving message from renderer: 298.853
+  (Session info: chrome=145.0.7632.160)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff62bd0aa55
+	0x7ff62ba68630
+	0x7ff62b7fd75d
+	0x7ff62b7ea3d9
+	0x7ff62b7ea0c1
+	0x7ff62b7e7d0b
+	0x7ff62b7e862f
+	0x7ff62b7f7b0a
+	0x7ff62b80e9f7
+	0x7ff62b81612a
+	0x7ff62b7e8df1
+	0x7ff62b80e72b
+	0x7ff62b8a5cc1
+	0x7ff62b849098
+	0x7ff62b849f83
+	0x7ff62bd37810
+	0x7ff62bd31afd
+	0x7ff62bd52c1a
+	0x7ff62ba83345
+	0x7ff62ba8b81c
+	0x7ff62ba71924
+	0x7ff62ba71ad6
+	0x7ff62ba57e47
+	0x7ffe0db5e8d7
+	0x7ffe0f12c40c
+</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2102,12 +2160,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>£28.00</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/celotex-pl4000-37-5mm (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001EE40656450&gt;, 'Connection to build4less.co.uk timed out. (connect timeout=30)'))</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>£28.00</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2162,7 +2220,36 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>£28.03</t>
+          <t xml:space="preserve">Error: Message: timeout: Timed out receiving message from renderer: 298.975
+  (Session info: chrome=145.0.7632.160)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff62bd0aa55
+	0x7ff62ba68630
+	0x7ff62b7fd75d
+	0x7ff62b7ea3d9
+	0x7ff62b7ea0c1
+	0x7ff62b7e7d0b
+	0x7ff62b7e862f
+	0x7ff62b7f7b0a
+	0x7ff62b80e9f7
+	0x7ff62b81612a
+	0x7ff62b7e8df1
+	0x7ff62b80e72b
+	0x7ff62b8a5cc1
+	0x7ff62b849098
+	0x7ff62b849f83
+	0x7ff62bd37810
+	0x7ff62bd31afd
+	0x7ff62bd52c1a
+	0x7ff62ba83345
+	0x7ff62ba8b81c
+	0x7ff62ba71924
+	0x7ff62ba71ad6
+	0x7ff62ba57e47
+	0x7ffe0db5e8d7
+	0x7ffe0f12c40c
+</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2346,7 +2433,36 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>£37.07</t>
+          <t xml:space="preserve">Error: Message: timeout: Timed out receiving message from renderer: 299.037
+  (Session info: chrome=145.0.7632.160)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff62bd0aa55
+	0x7ff62ba68630
+	0x7ff62b7fd75d
+	0x7ff62b7ea3d9
+	0x7ff62b7ea0c1
+	0x7ff62b7e7d0b
+	0x7ff62b7e862f
+	0x7ff62b7f7b0a
+	0x7ff62b80e9f7
+	0x7ff62b81612a
+	0x7ff62b7e8df1
+	0x7ff62b80e72b
+	0x7ff62b8a5cc1
+	0x7ff62b849098
+	0x7ff62b849f83
+	0x7ff62bd37810
+	0x7ff62bd31afd
+	0x7ff62bd52c1a
+	0x7ff62ba83345
+	0x7ff62ba8b81c
+	0x7ff62ba71924
+	0x7ff62ba71ad6
+	0x7ff62ba57e47
+	0x7ffe0db5e8d7
+	0x7ffe0f12c40c
+</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
